--- a/output/graficos_dimensiones/comunal_d_env_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_maule.xlsx
@@ -78,12 +78,12 @@
     <t xml:space="preserve">Longaví</t>
   </si>
   <si>
+    <t xml:space="preserve">Rauco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Río Claro</t>
   </si>
   <si>
-    <t xml:space="preserve">Rauco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linares</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -565,7 +565,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>210.28</v>
+        <v>228.21</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>170.16</v>
+        <v>184.35</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>168.13</v>
+        <v>180.46</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>166.38</v>
+        <v>180.22</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>156.22</v>
+        <v>166.89</v>
       </c>
     </row>
     <row r="7">
@@ -650,7 +650,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>150.36</v>
+        <v>165.53</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +667,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>145.64</v>
+        <v>156.12</v>
       </c>
     </row>
     <row r="9">
@@ -684,7 +684,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>144.91</v>
+        <v>155.99</v>
       </c>
     </row>
     <row r="10">
@@ -701,7 +701,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>136.14</v>
+        <v>146.17</v>
       </c>
     </row>
     <row r="11">
@@ -718,7 +718,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>133.87</v>
+        <v>143.67</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>129.66</v>
+        <v>138.51</v>
       </c>
     </row>
     <row r="13">
@@ -752,7 +752,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>128.28</v>
+        <v>138.11</v>
       </c>
     </row>
     <row r="14">
@@ -769,7 +769,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>127.77</v>
+        <v>137.91</v>
       </c>
     </row>
     <row r="15">
@@ -786,7 +786,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>124.43</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="16">
@@ -797,13 +797,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7108</v>
+        <v>7305</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>124.05</v>
+        <v>134.56</v>
       </c>
     </row>
     <row r="17">
@@ -814,13 +814,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7305</v>
+        <v>7108</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>123.79</v>
+        <v>133.39</v>
       </c>
     </row>
     <row r="18">
@@ -837,7 +837,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>121.09</v>
+        <v>129.82</v>
       </c>
     </row>
     <row r="19">
@@ -854,7 +854,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>120.92</v>
+        <v>129.42</v>
       </c>
     </row>
     <row r="20">
@@ -871,7 +871,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>119.35</v>
+        <v>128.68</v>
       </c>
     </row>
     <row r="21">
@@ -888,7 +888,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>117.59</v>
+        <v>127.09</v>
       </c>
     </row>
     <row r="22">
@@ -905,7 +905,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>115.54</v>
+        <v>124.43</v>
       </c>
     </row>
     <row r="23">
@@ -922,7 +922,7 @@
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>113.26</v>
+        <v>121.85</v>
       </c>
     </row>
     <row r="24">
@@ -939,7 +939,7 @@
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>112.1</v>
+        <v>120.97</v>
       </c>
     </row>
     <row r="25">
@@ -956,7 +956,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>111.46</v>
+        <v>120.09</v>
       </c>
     </row>
     <row r="26">
@@ -973,7 +973,7 @@
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>110.15</v>
+        <v>118.88</v>
       </c>
     </row>
     <row r="27">
@@ -990,7 +990,7 @@
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>109.92</v>
+        <v>117.87</v>
       </c>
     </row>
     <row r="28">
@@ -1007,7 +1007,7 @@
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>109.36</v>
+        <v>117.55</v>
       </c>
     </row>
     <row r="29">
@@ -1024,7 +1024,7 @@
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>98.85</v>
+        <v>106.22</v>
       </c>
     </row>
     <row r="30">
@@ -1041,7 +1041,7 @@
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>97.08</v>
+        <v>104.86</v>
       </c>
     </row>
     <row r="31">
@@ -1058,7 +1058,7 @@
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>52.81</v>
+        <v>56.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:26</t>
+    <t xml:space="preserve">2026-10-05 16:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
